--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -18611,34 +18611,34 @@
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
-        <v>25851000</v>
+        <v>24946200</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>33228</v>
+        <v>32065</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
-          <t>7.60%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K282" s="5" t="n">
-        <v>23885900</v>
+        <v>24946200</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>30702</v>
+        <v>32065</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 (減3.5%) + 代繳從價印花稅</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N282" s="3" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -29127,12 +29127,12 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B17" s="20" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 778呎 (3房)
-$2585万
-$33,228/呎
-(在售)</t>
+$2495万
+$32,065/呎
+(26年-09月-04日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -18607,7 +18607,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -18623,7 +18623,7 @@
         <v>24946200</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>32065</v>
+        <v>32106</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>24946200</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>32065</v>
+        <v>32106</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
@@ -20099,34 +20099,34 @@
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G306" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="H306" s="5" t="n">
-        <v>25544000</v>
+        <v>24649900</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>32833</v>
+        <v>31684</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K306" s="5" t="n">
-        <v>20946080</v>
+        <v>24649900</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>26923</v>
+        <v>31684</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
-          <t>現金付款計劃 - 90天成交</t>
+          <t>-</t>
         </is>
       </c>
       <c r="N306" s="3" t="inlineStr">
@@ -28400,7 +28400,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -28410,7 +28410,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -29129,9 +29129,9 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 778呎 (3房)
+          <t>A | 777呎 (3房)
 $2495万
-$32,065/呎
+$32,106/呎
 (26年-09月-04日)</t>
         </is>
       </c>
@@ -29347,12 +29347,12 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 778呎 (3房)
-$2554万
-$32,833/呎
-(在售)</t>
+$2465万
+$31,684/呎
+(26年-10月-04日)</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -18616,7 +18616,7 @@
       </c>
       <c r="G282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="H282" s="5" t="n">
@@ -29132,7 +29132,7 @@
           <t>A | 777呎 (3房)
 $2495万
 $32,106/呎
-(26年-09月-04日)</t>
+(26年-10月-05日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -20095,7 +20095,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>24649900</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>31684</v>
+        <v>31724</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -20122,7 +20122,7 @@
         <v>24649900</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>31684</v>
+        <v>31724</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -29349,9 +29349,9 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>A | 778呎 (3房)
+          <t>A | 777呎 (3房)
 $2465万
-$31,684/呎
+$31,724/呎
 (26年-10月-04日)</t>
         </is>
       </c>

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -5363,38 +5363,30 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="n">
+        <v>25788000</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>33232</v>
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="K74" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="L74" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="K74" s="5" t="n">
+        <v>25788000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>33232</v>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
@@ -5403,7 +5395,7 @@
       </c>
       <c r="N74" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -26409,7 +26401,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -26419,7 +26411,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>138</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -27081,12 +27073,12 @@
           <t>28</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 776呎 (3房)
-招标单位
--
-(在售)</t>
+$2579万
+$33,232/呎
+(26年-10月-23日)</t>
         </is>
       </c>
       <c r="C16" s="21" t="inlineStr">

--- a/files/九龙-启德-The Henley III.xlsx
+++ b/files/九龙-启德-The Henley III.xlsx
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
@@ -3071,7 +3071,7 @@
         <v>25996000</v>
       </c>
       <c r="I38" s="5" t="n">
-        <v>33543</v>
+        <v>33500</v>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>25996000</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>33543</v>
+        <v>33500</v>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -3451,7 +3451,7 @@
         <v>25918400</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>33443</v>
+        <v>33400</v>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
@@ -3462,7 +3462,7 @@
         <v>25918400</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>33443</v>
+        <v>33400</v>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>25220000</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>32542</v>
+        <v>32500</v>
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
@@ -5006,7 +5006,7 @@
         <v>25220000</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>32542</v>
+        <v>32500</v>
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
@@ -6903,7 +6903,7 @@
         </is>
       </c>
       <c r="E98" s="4" t="n">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="F98" s="3" t="inlineStr">
         <is>
@@ -6919,7 +6919,7 @@
         <v>24832000</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>32041</v>
+        <v>32000</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>24832000</v>
       </c>
       <c r="L98" s="5" t="n">
-        <v>32041</v>
+        <v>32000</v>
       </c>
       <c r="M98" s="3" t="inlineStr">
         <is>
@@ -14507,7 +14507,7 @@
         </is>
       </c>
       <c r="E216" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F216" s="3" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>25724100</v>
       </c>
       <c r="I216" s="5" t="n">
-        <v>33107</v>
+        <v>33064</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>25724100</v>
       </c>
       <c r="L216" s="5" t="n">
-        <v>33107</v>
+        <v>33064</v>
       </c>
       <c r="M216" s="3" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="E228" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F228" s="3" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>25819400</v>
       </c>
       <c r="I228" s="5" t="n">
-        <v>33230</v>
+        <v>33187</v>
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>25819400</v>
       </c>
       <c r="L228" s="5" t="n">
-        <v>33230</v>
+        <v>33187</v>
       </c>
       <c r="M228" s="3" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         </is>
       </c>
       <c r="E234" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F234" s="3" t="inlineStr">
         <is>
@@ -15639,7 +15639,7 @@
         <v>25213900</v>
       </c>
       <c r="I234" s="5" t="n">
-        <v>32450</v>
+        <v>32409</v>
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>25213900</v>
       </c>
       <c r="L234" s="5" t="n">
-        <v>32450</v>
+        <v>32409</v>
       </c>
       <c r="M234" s="3" t="inlineStr">
         <is>
@@ -16367,7 +16367,7 @@
         </is>
       </c>
       <c r="E246" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F246" s="3" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>25068600</v>
       </c>
       <c r="I246" s="5" t="n">
-        <v>32263</v>
+        <v>32222</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -16394,7 +16394,7 @@
         <v>25068600</v>
       </c>
       <c r="L246" s="5" t="n">
-        <v>32263</v>
+        <v>32222</v>
       </c>
       <c r="M246" s="3" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         </is>
       </c>
       <c r="E258" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F258" s="3" t="inlineStr">
         <is>
@@ -17127,7 +17127,7 @@
         <v>25315800</v>
       </c>
       <c r="I258" s="5" t="n">
-        <v>32581</v>
+        <v>32540</v>
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>25315800</v>
       </c>
       <c r="L258" s="5" t="n">
-        <v>32581</v>
+        <v>32540</v>
       </c>
       <c r="M258" s="3" t="inlineStr">
         <is>
@@ -17483,7 +17483,7 @@
         </is>
       </c>
       <c r="E264" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F264" s="3" t="inlineStr">
         <is>
@@ -17499,7 +17499,7 @@
         <v>24849100</v>
       </c>
       <c r="I264" s="5" t="n">
-        <v>31981</v>
+        <v>31940</v>
       </c>
       <c r="J264" s="3" t="inlineStr">
         <is>
@@ -17510,7 +17510,7 @@
         <v>24849100</v>
       </c>
       <c r="L264" s="5" t="n">
-        <v>31981</v>
+        <v>31940</v>
       </c>
       <c r="M264" s="3" t="inlineStr">
         <is>
@@ -17855,7 +17855,7 @@
         </is>
       </c>
       <c r="E270" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F270" s="3" t="inlineStr">
         <is>
@@ -17871,7 +17871,7 @@
         <v>24776900</v>
       </c>
       <c r="I270" s="5" t="n">
-        <v>31888</v>
+        <v>31847</v>
       </c>
       <c r="J270" s="3" t="inlineStr">
         <is>
@@ -17882,7 +17882,7 @@
         <v>24776900</v>
       </c>
       <c r="L270" s="5" t="n">
-        <v>31888</v>
+        <v>31847</v>
       </c>
       <c r="M270" s="3" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         </is>
       </c>
       <c r="E276" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F276" s="3" t="inlineStr">
         <is>
@@ -18243,7 +18243,7 @@
         <v>24703800</v>
       </c>
       <c r="I276" s="5" t="n">
-        <v>31794</v>
+        <v>31753</v>
       </c>
       <c r="J276" s="3" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>24703800</v>
       </c>
       <c r="L276" s="5" t="n">
-        <v>31794</v>
+        <v>31753</v>
       </c>
       <c r="M276" s="3" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         </is>
       </c>
       <c r="E282" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F282" s="3" t="inlineStr">
         <is>
@@ -18615,7 +18615,7 @@
         <v>24946200</v>
       </c>
       <c r="I282" s="5" t="n">
-        <v>32106</v>
+        <v>32065</v>
       </c>
       <c r="J282" s="3" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>24946200</v>
       </c>
       <c r="L282" s="5" t="n">
-        <v>32106</v>
+        <v>32065</v>
       </c>
       <c r="M282" s="3" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         </is>
       </c>
       <c r="E288" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F288" s="3" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>24485300</v>
       </c>
       <c r="I288" s="5" t="n">
-        <v>31513</v>
+        <v>31472</v>
       </c>
       <c r="J288" s="3" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>24485300</v>
       </c>
       <c r="L288" s="5" t="n">
-        <v>31513</v>
+        <v>31472</v>
       </c>
       <c r="M288" s="3" t="inlineStr">
         <is>
@@ -20087,7 +20087,7 @@
         </is>
       </c>
       <c r="E306" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F306" s="3" t="inlineStr">
         <is>
@@ -20103,7 +20103,7 @@
         <v>24649900</v>
       </c>
       <c r="I306" s="5" t="n">
-        <v>31724</v>
+        <v>31684</v>
       </c>
       <c r="J306" s="3" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>24649900</v>
       </c>
       <c r="L306" s="5" t="n">
-        <v>31724</v>
+        <v>31684</v>
       </c>
       <c r="M306" s="3" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
         </is>
       </c>
       <c r="E324" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F324" s="3" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>24047300</v>
       </c>
       <c r="I324" s="5" t="n">
-        <v>30949</v>
+        <v>30909</v>
       </c>
       <c r="J324" s="3" t="inlineStr">
         <is>
@@ -21230,7 +21230,7 @@
         <v>24047300</v>
       </c>
       <c r="L324" s="5" t="n">
-        <v>30949</v>
+        <v>30909</v>
       </c>
       <c r="M324" s="3" t="inlineStr">
         <is>
@@ -21947,7 +21947,7 @@
         </is>
       </c>
       <c r="E336" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F336" s="3" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>23975100</v>
       </c>
       <c r="I336" s="5" t="n">
-        <v>30856</v>
+        <v>30816</v>
       </c>
       <c r="J336" s="3" t="inlineStr">
         <is>
@@ -21974,7 +21974,7 @@
         <v>23975100</v>
       </c>
       <c r="L336" s="5" t="n">
-        <v>30856</v>
+        <v>30816</v>
       </c>
       <c r="M336" s="3" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         </is>
       </c>
       <c r="E354" s="4" t="n">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F354" s="3" t="inlineStr">
         <is>
@@ -23079,7 +23079,7 @@
         <v>23756600</v>
       </c>
       <c r="I354" s="5" t="n">
-        <v>30575</v>
+        <v>30535</v>
       </c>
       <c r="J354" s="3" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>23756600</v>
       </c>
       <c r="L354" s="5" t="n">
-        <v>30575</v>
+        <v>30535</v>
       </c>
       <c r="M354" s="3" t="inlineStr">
         <is>
@@ -26745,9 +26745,9 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>A | 775呎 (3房)
+          <t>A | 776呎 (3房)
 $2600万
-$33,543/呎
+$33,500/呎
 (26年-08月-18日)</t>
         </is>
       </c>
@@ -26800,9 +26800,9 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 775呎 (3房)
+          <t>A | 776呎 (3房)
 $2592万
-$33,443/呎
+$33,400/呎
 (26年-05月-26日)</t>
         </is>
       </c>
@@ -27020,9 +27020,9 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 775呎 (3房)
+          <t>A | 776呎 (3房)
 $2522万
-$32,542/呎
+$32,500/呎
 (26年-05月-12日)</t>
         </is>
       </c>
@@ -27295,9 +27295,9 @@
       </c>
       <c r="B20" s="22" t="inlineStr">
         <is>
-          <t>A | 775呎 (3房)
+          <t>A | 776呎 (3房)
 $2483万
-$32,041/呎
+$32,000/呎
 (26年-03月-26日)</t>
         </is>
       </c>
@@ -28516,9 +28516,9 @@
       </c>
       <c r="B6" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2572万
-$33,107/呎
+$33,064/呎
 (26年-02月-11日)</t>
         </is>
       </c>
@@ -28626,9 +28626,9 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2582万
-$33,230/呎
+$33,187/呎
 (23年-01月-26日)</t>
         </is>
       </c>
@@ -28681,9 +28681,9 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2521万
-$32,450/呎
+$32,409/呎
 (22年-06月-13日)</t>
         </is>
       </c>
@@ -28791,9 +28791,9 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2507万
-$32,263/呎
+$32,222/呎
 (24年-10月-02日)</t>
         </is>
       </c>
@@ -28901,9 +28901,9 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2532万
-$32,581/呎
+$32,540/呎
 (24年-05月-28日)</t>
         </is>
       </c>
@@ -28956,9 +28956,9 @@
       </c>
       <c r="B14" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2485万
-$31,981/呎
+$31,940/呎
 (24年-12月-03日)</t>
         </is>
       </c>
@@ -29011,9 +29011,9 @@
       </c>
       <c r="B15" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2478万
-$31,888/呎
+$31,847/呎
 (25年-12月-08日)</t>
         </is>
       </c>
@@ -29066,9 +29066,9 @@
       </c>
       <c r="B16" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2470万
-$31,794/呎
+$31,753/呎
 (26年-06月-10日)</t>
         </is>
       </c>
@@ -29121,9 +29121,9 @@
       </c>
       <c r="B17" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2495万
-$32,106/呎
+$32,065/呎
 (26年-10月-05日)</t>
         </is>
       </c>
@@ -29176,9 +29176,9 @@
       </c>
       <c r="B18" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2449万
-$31,513/呎
+$31,472/呎
 (23年-06月-14日)</t>
         </is>
       </c>
@@ -29341,9 +29341,9 @@
       </c>
       <c r="B21" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2465万
-$31,724/呎
+$31,684/呎
 (26年-10月-04日)</t>
         </is>
       </c>
@@ -29506,9 +29506,9 @@
       </c>
       <c r="B24" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2405万
-$30,949/呎
+$30,909/呎
 (26年-01月-16日)</t>
         </is>
       </c>
@@ -29616,9 +29616,9 @@
       </c>
       <c r="B26" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2398万
-$30,856/呎
+$30,816/呎
 (26年-06月-17日)</t>
         </is>
       </c>
@@ -29781,9 +29781,9 @@
       </c>
       <c r="B29" s="22" t="inlineStr">
         <is>
-          <t>A | 777呎 (3房)
+          <t>A | 778呎 (3房)
 $2376万
-$30,575/呎
+$30,535/呎
 (25年-11月-10日)</t>
         </is>
       </c>
